--- a/e_commerce_forms/006_lockdown_food_order_form--e_commerce_forms.xlsx
+++ b/e_commerce_forms/006_lockdown_food_order_form--e_commerce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1041,8 +1041,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cancel'}</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cancel'}</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'chicken'}</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Chicken'}</t>
+          <t>Chicken</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fish'}</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fish'}</t>
+          <t>Fish</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'veggie'}</t>
+          <t>veggie</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Veggie'}</t>
+          <t>Veggie</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pepperoni'}</t>
+          <t>pepperoni</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pepperoni'}</t>
+          <t>Pepperoni</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mushroom'}</t>
+          <t>mushroom</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mushroom'}</t>
+          <t>Mushroom</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'veggie'}</t>
+          <t>veggie</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Veggie'}</t>
+          <t>Veggie</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'tomato'}</t>
+          <t>tomato</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Tomato'}</t>
+          <t>Tomato</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cucumber'}</t>
+          <t>cucumber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cucumber'}</t>
+          <t>Cucumber</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'avocado'}</t>
+          <t>avocado</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Avocado'}</t>
+          <t>Avocado</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'beef'}</t>
+          <t>beef</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Beef'}</t>
+          <t>Beef</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'chicken'}</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Chicken'}</t>
+          <t>Chicken</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'veggie'}</t>
+          <t>veggie</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Veggie'}</t>
+          <t>Veggie</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'blt'}</t>
+          <t>blt</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'BLT'}</t>
+          <t>BLT</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'grilled_cheese'}</t>
+          <t>grilled_cheese</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Grilled Cheese'}</t>
+          <t>Grilled Cheese</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'ham'}</t>
+          <t>ham</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Ham'}</t>
+          <t>Ham</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'water'}</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Water'}</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'juice'}</t>
+          <t>juice</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Juice'}</t>
+          <t>Juice</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'coffee'}</t>
+          <t>coffee</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Coffee'}</t>
+          <t>Coffee</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pie'}</t>
+          <t>pie</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pie'}</t>
+          <t>Pie</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cake'}</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cake'}</t>
+          <t>Cake</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'ice_cream'}</t>
+          <t>ice_cream</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Ice Cream'}</t>
+          <t>Ice Cream</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'salmon'}</t>
+          <t>salmon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Salmon'}</t>
+          <t>Salmon</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tuna'}</t>
+          <t>tuna</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tuna'}</t>
+          <t>Tuna</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'veggie'}</t>
+          <t>veggie</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Veggie'}</t>
+          <t>Veggie</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_"i'm_done"}</t>
+          <t>i'm_done</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': "I'm Done"}</t>
+          <t>I'm Done</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'save_and_exit'}</t>
+          <t>save_and_exit</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Save and Exit'}</t>
+          <t>Save and Exit</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'confirm'}</t>
+          <t>confirm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Confirm'}</t>
+          <t>Confirm</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cancel'}</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cancel'}</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
